--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,8 +505,7 @@
     <t>849: source value from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
   </si>
   <si>
-    <t>Chem.LabChem.ShortAccessionNumber
-Chem.PatientLabChem.ShortAccessionNumber</t>
+    <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
   </si>
   <si>
     <t>Specimen.status</t>
@@ -1538,7 +1537,7 @@
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="54.51171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="166.86328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="44.08203125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="81.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,12 +250,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -496,16 +496,16 @@
     <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
   </si>
   <si>
+    <t>849: source value from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
+  </si>
+  <si>
+    <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
+  </si>
+  <si>
     <t>.participation[typeCode=SBJ].act[classCode=ACSN, moodCode=EVN].id</t>
   </si>
   <si>
     <t>SPM-30 (v2.7+)</t>
-  </si>
-  <si>
-    <t>849: source value from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
-  </si>
-  <si>
-    <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
   </si>
   <si>
     <t>Specimen.status</t>
@@ -656,13 +656,13 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>859: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - NAME (#63.04-.35 &gt; 63.07-9 &gt; 62-.01)</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>859: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - NAME (#63.04-.35 &gt; 63.07-9 &gt; 62-.01)</t>
   </si>
   <si>
     <t>Specimen.subject</t>
@@ -1533,11 +1533,11 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="99.94921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="54.51171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="166.86328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="81.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="166.86328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="81.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.94921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="54.51171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1765,13 +1765,13 @@
         <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>78</v>
@@ -2348,13 +2348,13 @@
         <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2465,13 +2465,13 @@
         <v>78</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2582,13 +2582,13 @@
         <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2701,13 +2701,13 @@
         <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM10" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2816,19 +2816,19 @@
         <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -2934,13 +2934,13 @@
         <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>157</v>
@@ -3048,19 +3048,19 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -3165,19 +3165,19 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3280,13 +3280,13 @@
         <v>78</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3397,13 +3397,13 @@
         <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3516,19 +3516,19 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3644,10 +3644,10 @@
         <v>207</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -3752,16 +3752,16 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -3867,19 +3867,19 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3984,13 +3984,13 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4101,19 +4101,19 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4216,19 +4216,19 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -4331,13 +4331,13 @@
         <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4448,13 +4448,13 @@
         <v>138</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4567,13 +4567,13 @@
         <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4682,19 +4682,19 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -4797,19 +4797,19 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4915,13 +4915,13 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5027,19 +5027,19 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5142,19 +5142,19 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5259,19 +5259,19 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5384,13 +5384,13 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -5493,13 +5493,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5608,13 +5608,13 @@
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5725,13 +5725,13 @@
         <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -5844,13 +5844,13 @@
         <v>138</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -5959,13 +5959,13 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6074,13 +6074,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6189,19 +6189,19 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -6304,13 +6304,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6419,13 +6419,13 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6534,13 +6534,13 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6651,13 +6651,13 @@
         <v>138</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6770,13 +6770,13 @@
         <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -6885,19 +6885,19 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7000,13 +7000,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7115,19 +7115,19 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -7230,19 +7230,19 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7345,19 +7345,19 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -7460,19 +7460,19 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -7585,13 +7585,13 @@
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -7694,19 +7694,19 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to Specimen</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (63.04) to Specimen</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -496,7 +496,7 @@
     <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
   </si>
   <si>
-    <t>849: source value from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
+    <t>849: source value from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (63.04-.06)</t>
   </si>
   <si>
     <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
@@ -656,7 +656,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>859: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - NAME (#63.04-.35 &gt; 63.07-9 &gt; 62-.01)</t>
+    <t>859: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - COLLECTION SAMPLE &gt; COLLECTION SAMPLE - NAME (63.04-.35 &gt; 63.07-9 &gt; 62-.01)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1533,7 +1533,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="166.86328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="165.32421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="81.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.94921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsChemhemtoxriaserSpecimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
